--- a/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -48,13 +48,118 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>3.</t>
+    <t>Status (Mobile)</t>
+  </si>
+  <si>
+    <t>Test Case Data</t>
+  </si>
+  <si>
+    <t>TC-SMK-1</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>TC-SMK-2</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>1. Choose new account registration</t>
+  </si>
+  <si>
+    <t>Email: takimawot555@gmail.com Password: 1234</t>
+  </si>
+  <si>
+    <t>2. Enter email address, name and password</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page  2. Click on Sign In button (top, right)</t>
+  </si>
+  <si>
+    <t>Error message about password (must be more than 6 letters)</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>The web site do not react on wrong email</t>
+  </si>
+  <si>
+    <t>3. Input wrong password verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message about wrong password matching </t>
+  </si>
+  <si>
+    <t>TC-SMK-3</t>
+  </si>
+  <si>
+    <t>Email: takimawot555@gmail.com Password: 123456</t>
+  </si>
+  <si>
+    <t>Email: takimawot@gmail.com Password: 123456</t>
+  </si>
+  <si>
+    <t>Successful registration</t>
+  </si>
+  <si>
+    <t>Sign In</t>
+  </si>
+  <si>
+    <t>TC-SMK-4</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page  2. Sign out (if account is signed in)</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on invalid inputs for registration</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on valid inputs for registration</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on invalid password for signing in</t>
+  </si>
+  <si>
+    <t>1. Write the email address</t>
+  </si>
+  <si>
+    <t>2. Wait until password entering line appears</t>
+  </si>
+  <si>
+    <t>3. Enter wrong password</t>
+  </si>
+  <si>
+    <t>Email: takimawot@gmail.com Password: 213456</t>
+  </si>
+  <si>
+    <t>Error message about incorrect password</t>
+  </si>
+  <si>
+    <t>TC-SMK-5</t>
+  </si>
+  <si>
+    <t>3. Enter password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Successful log in </t>
+  </si>
+  <si>
+    <t>Log In</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page  2. Sign out (if account is logged in)</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on invalid password for logging in</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on valid password for logging in</t>
   </si>
 </sst>
 </file>
@@ -142,22 +247,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -438,87 +567,485 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J5"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="30.109375" customWidth="1"/>
+    <col min="6" max="6" width="36.77734375" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" customWidth="1"/>
+    <col min="8" max="8" width="26.88671875" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" customWidth="1"/>
+    <col min="11" max="11" width="18.21875" customWidth="1"/>
+    <col min="13" max="13" width="10.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="B2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="H3:H5"/>
+  <mergeCells count="60">
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="101">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -78,9 +78,6 @@
     <t>2. Enter email address, name and password</t>
   </si>
   <si>
-    <t>1. Entering the Amazon main page  2. Click on Sign In button (top, right)</t>
-  </si>
-  <si>
     <t>Error message about password (must be more than 6 letters)</t>
   </si>
   <si>
@@ -108,24 +105,15 @@
     <t>Successful registration</t>
   </si>
   <si>
-    <t>Sign In</t>
-  </si>
-  <si>
     <t>TC-SMK-4</t>
   </si>
   <si>
-    <t>1. Entering the Amazon main page  2. Sign out (if account is signed in)</t>
-  </si>
-  <si>
     <t>Verification of application reaction on invalid inputs for registration</t>
   </si>
   <si>
     <t>Verification of application reaction on valid inputs for registration</t>
   </si>
   <si>
-    <t>Verification of application reaction on invalid password for signing in</t>
-  </si>
-  <si>
     <t>1. Write the email address</t>
   </si>
   <si>
@@ -153,25 +141,222 @@
     <t>Log In</t>
   </si>
   <si>
-    <t>1. Entering the Amazon main page  2. Sign out (if account is logged in)</t>
-  </si>
-  <si>
     <t>Verification of application reaction on invalid password for logging in</t>
   </si>
   <si>
     <t>Verification of application reaction on valid password for logging in</t>
+  </si>
+  <si>
+    <t>TC-SMK-6</t>
+  </si>
+  <si>
+    <t>Product Searching</t>
+  </si>
+  <si>
+    <t>1. Write the wrong word</t>
+  </si>
+  <si>
+    <t>2. Check the result</t>
+  </si>
+  <si>
+    <t>3. Repeat step 1 and step 2</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on totally invalid words for searching</t>
+  </si>
+  <si>
+    <t>Error message about incorrect words, or no results found, or show the most similar variants</t>
+  </si>
+  <si>
+    <t>The website shows the most similar potential results</t>
+  </si>
+  <si>
+    <t>TC-SMK-7</t>
+  </si>
+  <si>
+    <t>1. Write the almost right word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Words: compu(io)ter, bath(hhhht)room, (g)elmet </t>
+  </si>
+  <si>
+    <t>Show the most similar results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The website also changes the words from the search line to the correct ones (compuioter -&gt; computer) </t>
+  </si>
+  <si>
+    <t>Verification of application reaction on invalid (almost valid) words for searching</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on valid words for searching</t>
+  </si>
+  <si>
+    <t>1. Write the correct word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Words: computer, bathroom, helmet </t>
+  </si>
+  <si>
+    <t>Show the correct results</t>
+  </si>
+  <si>
+    <t>TC-SMK-8</t>
+  </si>
+  <si>
+    <t>Product Filtering</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page                  2. Choose the product type (gaming mouse)</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page                   2. Enter the Search words</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page                  2. Enter the Search words</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page                    2. Enter the Search words</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page                    2. Sign out (if account is logged in)</t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page                    2. Click on Sign In button (top, right)</t>
+  </si>
+  <si>
+    <t>Verification of "Sort by" function</t>
+  </si>
+  <si>
+    <t>1. Choose the sorting method</t>
+  </si>
+  <si>
+    <t>2. Verify if the result is sorting properly</t>
+  </si>
+  <si>
+    <t>Sorting Methods: Price (low to high), Price (high to low), Avg. Customer Review, Newest Arrivals, Best Sellers</t>
+  </si>
+  <si>
+    <t>Correct sorting output for each sorting method</t>
+  </si>
+  <si>
+    <t>Verification several departments sorting</t>
+  </si>
+  <si>
+    <t>1. Choose the department section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Change the department and repeat step 2 </t>
+  </si>
+  <si>
+    <t>Several Departments: Baby, Computer, Software, All Departments</t>
+  </si>
+  <si>
+    <t>Show the correct results from departments and not from others</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If the item is not from the chosen department that there is a notification alert:                                      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Showing results from All Departments                         No results for mouse in Baby</t>
+    </r>
+  </si>
+  <si>
+    <t>TC-SMK-9</t>
+  </si>
+  <si>
+    <t>TC-SMK-10</t>
+  </si>
+  <si>
+    <t>TC-SMK-11</t>
+  </si>
+  <si>
+    <t>TC-SMK-12</t>
+  </si>
+  <si>
+    <t>Verification of proper price-based filtering</t>
+  </si>
+  <si>
+    <t>1. Choose the price boundaries</t>
+  </si>
+  <si>
+    <t>Prices in USD: 0-12, 350-760, 6000-8100+</t>
+  </si>
+  <si>
+    <t>2. Check if products are inside the boundaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Words: bbbabdfhabh, iahayvg, ufabfha, oajojoan+G10:G18bhka </t>
+  </si>
+  <si>
+    <t>3. Repeat step 1 and step 2 for other prices</t>
+  </si>
+  <si>
+    <t>Show only the products that are between chosen prices</t>
+  </si>
+  <si>
+    <t>Verification of application reaction on other types of filtering</t>
+  </si>
+  <si>
+    <t>Bug report</t>
+  </si>
+  <si>
+    <t>Wireless in USB</t>
+  </si>
+  <si>
+    <t>Black picture, white color</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Show the correct results after filtering</t>
+  </si>
+  <si>
+    <t>1. Choose the filtering aspect</t>
+  </si>
+  <si>
+    <t>Filtering aspects: Mouse Interface - USB; Brands - Logitech; Color - White</t>
+  </si>
+  <si>
+    <t>2. Check the results</t>
+  </si>
+  <si>
+    <t>3. Change the aspects and repeat previous steps</t>
+  </si>
+  <si>
+    <t>Show wireless mouses after choosing the USB;       Show the black picture of a mouse with color white</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -247,15 +432,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -263,13 +445,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -281,10 +460,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -567,21 +755,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="30.109375" customWidth="1"/>
-    <col min="6" max="6" width="36.77734375" customWidth="1"/>
-    <col min="7" max="7" width="28.44140625" customWidth="1"/>
-    <col min="8" max="8" width="26.88671875" customWidth="1"/>
+    <col min="4" max="4" width="37.109375" customWidth="1"/>
+    <col min="5" max="5" width="29.44140625" customWidth="1"/>
+    <col min="6" max="6" width="40.6640625" customWidth="1"/>
+    <col min="7" max="7" width="34.21875" customWidth="1"/>
+    <col min="8" max="8" width="28.33203125" customWidth="1"/>
     <col min="9" max="9" width="7.5546875" customWidth="1"/>
     <col min="10" max="10" width="13.77734375" customWidth="1"/>
-    <col min="11" max="11" width="18.21875" customWidth="1"/>
-    <col min="13" max="13" width="10.109375" customWidth="1"/>
+    <col min="11" max="11" width="44.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -620,379 +809,1167 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="I2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="15"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="11" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="G11" s="14"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="D16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="14"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="14"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="14"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="D22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="11"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="G23" s="14"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="D25" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="8"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="13"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="14"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="13"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="L34" t="s">
+        <v>91</v>
+      </c>
+      <c r="M34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="14"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="12"/>
+      <c r="L35" t="s">
+        <v>91</v>
+      </c>
+      <c r="M35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="14"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" s="14"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="12"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G48" s="14"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="13"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G50" s="14"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="14"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="9"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G56" s="14"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="12"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G57" s="14"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="I13:I15"/>
+  <mergeCells count="160">
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="J55:J57"/>
+    <mergeCell ref="K55:K57"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="H52:H54"/>
+    <mergeCell ref="I52:I54"/>
+    <mergeCell ref="J52:J54"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="H49:H51"/>
+    <mergeCell ref="I49:I51"/>
+    <mergeCell ref="J49:J51"/>
+    <mergeCell ref="K49:K51"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="I46:I48"/>
+    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="H34:H36"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="K34:K36"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="K31:K33"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="J28:J30"/>
+    <mergeCell ref="K28:K30"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="K25:K27"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="J4:J6"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="B10:B12"/>
@@ -1009,44 +1986,15 @@
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:J9"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="I13:I15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="123">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -336,6 +336,72 @@
   </si>
   <si>
     <t>Show wireless mouses after choosing the USB;       Show the black picture of a mouse with color white</t>
+  </si>
+  <si>
+    <t>TC-SMK-13</t>
+  </si>
+  <si>
+    <t>Cart Management</t>
+  </si>
+  <si>
+    <t>Verification of application carting system</t>
+  </si>
+  <si>
+    <t>1. Click on Add to the Cart button</t>
+  </si>
+  <si>
+    <t>2. Check if the product is in cart</t>
+  </si>
+  <si>
+    <t>3. Repeat the steps with other products</t>
+  </si>
+  <si>
+    <t>All items are in cart now</t>
+  </si>
+  <si>
+    <t>TC-SMK-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Entering the Amazon main page                  2. Choose any product </t>
+  </si>
+  <si>
+    <t>1. Entering the Amazon main page                  2. Choose any product and add it to the cart  3. Go to cart</t>
+  </si>
+  <si>
+    <t>Verification of application carting system (deletion of product)</t>
+  </si>
+  <si>
+    <t>1. Choose the product and click on Delete button</t>
+  </si>
+  <si>
+    <t>2. Check if the product is now deleted from cart</t>
+  </si>
+  <si>
+    <t>All items are now deleted from the cart</t>
+  </si>
+  <si>
+    <t>TC-SMK-15</t>
+  </si>
+  <si>
+    <t>Checkout Processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Entering the Amazon main page                  2. Choose the product </t>
+  </si>
+  <si>
+    <t>Verification of application behavior on checkout and before the payment</t>
+  </si>
+  <si>
+    <t>1. Add the product to the cart</t>
+  </si>
+  <si>
+    <t>2. Go to the cart</t>
+  </si>
+  <si>
+    <t>3.Click on "Proceed the Checkout" button</t>
+  </si>
+  <si>
+    <t>Show the page with all information about the items payment</t>
   </si>
 </sst>
 </file>
@@ -368,7 +434,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -428,11 +494,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -451,13 +526,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -469,11 +541,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -759,13 +857,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
     <col min="3" max="3" width="13.109375" customWidth="1"/>
     <col min="4" max="4" width="37.109375" customWidth="1"/>
     <col min="5" max="5" width="29.44140625" customWidth="1"/>
     <col min="6" max="6" width="40.6640625" customWidth="1"/>
     <col min="7" max="7" width="34.21875" customWidth="1"/>
-    <col min="8" max="8" width="28.33203125" customWidth="1"/>
+    <col min="8" max="8" width="30.44140625" customWidth="1"/>
     <col min="9" max="9" width="7.5546875" customWidth="1"/>
     <col min="10" max="10" width="13.77734375" customWidth="1"/>
     <col min="11" max="11" width="44.44140625" customWidth="1"/>
@@ -809,723 +907,723 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="11" t="s">
+      <c r="I2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="12"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="15"/>
+      <c r="I4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="16"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="15"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="16"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="15"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="15"/>
+      <c r="I7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="16"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="16"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="15"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="16"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>40</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="11"/>
+      <c r="I10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
       <c r="F11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="12"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="13"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="10" t="s">
         <v>41</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="11"/>
+      <c r="I13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="12"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="13"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="12"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>47</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="11" t="s">
+      <c r="I16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
       <c r="F17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="12"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
       <c r="F18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="13"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="11" t="s">
+      <c r="I19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="10" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
       <c r="F20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="14"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="12"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="11"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="14"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="13"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="10" t="s">
         <v>56</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="11"/>
+      <c r="I22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="10"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
       <c r="F23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="12"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
       <c r="F24" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="13"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="10" t="s">
         <v>68</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="11"/>
+      <c r="I25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="10"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
       <c r="F26" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="12"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
       <c r="F27" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="13"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="12"/>
     </row>
     <row r="28" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="10" t="s">
         <v>73</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="11" t="s">
+      <c r="I28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
       <c r="F29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="12"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
       <c r="F30" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="13"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="12"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>83</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="11"/>
+      <c r="I31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="10"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
       <c r="F32" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G32" s="14"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="12"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="11"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
       <c r="F33" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G33" s="14"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="13"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="12"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="10" t="s">
         <v>90</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="J34" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K34" s="10" t="s">
         <v>100</v>
       </c>
       <c r="L34" t="s">
@@ -1536,19 +1634,19 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
       <c r="F35" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="12"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="11"/>
       <c r="L35" t="s">
         <v>91</v>
       </c>
@@ -1557,398 +1655,404 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
       <c r="F36" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="13"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="8" t="s">
+      <c r="G36" s="9"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G47" s="14"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="12"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="13"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="8" t="s">
+      <c r="D37" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="9"/>
+      <c r="H37" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="10"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G38" s="9"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="11"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39" s="9"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G50" s="14"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="12"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="14"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="13"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="8" t="s">
+      <c r="D40" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="9"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="11"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G42" s="9"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="12"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H52" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K52" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G53" s="14"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="12"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G54" s="14"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="13"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G56" s="14"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="12"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G57" s="14"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="13"/>
+      <c r="D43" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G43" s="9"/>
+      <c r="H43" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="10"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G44" s="9"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="11"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G45" s="9"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="12"/>
+    </row>
+    <row r="46" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="23"/>
+      <c r="K46" s="23"/>
+    </row>
+    <row r="47" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+    </row>
+    <row r="48" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+    </row>
+    <row r="49" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+    </row>
+    <row r="50" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
+    </row>
+    <row r="51" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+    </row>
+    <row r="52" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+    </row>
+    <row r="53" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="24"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24"/>
+    </row>
+    <row r="54" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="24"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
+    </row>
+    <row r="55" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="24"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="24"/>
+    </row>
+    <row r="56" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="24"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="24"/>
+    </row>
+    <row r="57" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="160">
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="H55:H57"/>
-    <mergeCell ref="I55:I57"/>
-    <mergeCell ref="J55:J57"/>
-    <mergeCell ref="K55:K57"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="J52:J54"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="I49:I51"/>
-    <mergeCell ref="J49:J51"/>
-    <mergeCell ref="K49:K51"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="I46:I48"/>
-    <mergeCell ref="J46:J48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="H34:H36"/>
-    <mergeCell ref="I34:I36"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="K34:K36"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="K31:K33"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="J28:J30"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="K25:K27"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="K22:K24"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
+  <mergeCells count="150">
+    <mergeCell ref="K43:K45"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="H43:H45"/>
+    <mergeCell ref="I43:I45"/>
+    <mergeCell ref="J43:J45"/>
+    <mergeCell ref="K37:K39"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="I40:I42"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="K40:K42"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="I37:I39"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="I13:I15"/>
     <mergeCell ref="K4:K6"/>
     <mergeCell ref="K19:K21"/>
     <mergeCell ref="E2:E3"/>
@@ -1973,6 +2077,16 @@
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
     <mergeCell ref="E10:E12"/>
@@ -1980,19 +2094,72 @@
     <mergeCell ref="H10:H12"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="J10:J12"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="K25:K27"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="J28:J30"/>
+    <mergeCell ref="K28:K30"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="K31:K33"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="H34:H36"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="K34:K36"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Functional Testing Suite/Smoke Tests.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="120">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -306,15 +306,6 @@
   </si>
   <si>
     <t>Verification of application reaction on other types of filtering</t>
-  </si>
-  <si>
-    <t>Bug report</t>
-  </si>
-  <si>
-    <t>Wireless in USB</t>
-  </si>
-  <si>
-    <t>Black picture, white color</t>
   </si>
   <si>
     <t>Failed</t>
@@ -507,13 +498,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -525,30 +512,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -572,6 +535,35 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -872,1187 +864,1216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="23" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="10" t="s">
+      <c r="I2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="7" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="11"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="16"/>
     </row>
     <row r="4" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="16"/>
+      <c r="I4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="22"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="4" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="16"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="16"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="22"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="16"/>
+      <c r="I7" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="4" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="16"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="22"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="16"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="10"/>
+      <c r="I10" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="4" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="11"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="6" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="12"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="10"/>
+      <c r="I13" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="4" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="11"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="6" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="12"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="10" t="s">
+      <c r="I16" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="5" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="11"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="16"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="6" t="s">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="12"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="10" t="s">
+      <c r="I19" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="15" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="4" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="11"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="16"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="6" t="s">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="12"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="17"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="10"/>
+      <c r="I22" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="15"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="5" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="11"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="16"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="6" t="s">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="12"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="I25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="10"/>
+      <c r="I25" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="5" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="11"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="16"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="6" t="s">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="12"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="10" t="s">
+      <c r="I28" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="5" t="s">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="11"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="16"/>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="6" t="s">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="12"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="17"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="10"/>
+      <c r="I31" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="5" t="s">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="11"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="6" t="s">
+      <c r="G32" s="21"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="12"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
+      <c r="G33" s="21"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" s="21"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="16"/>
+    </row>
+    <row r="36" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="K34" s="10" t="s">
+      <c r="G36" s="21"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="L34" t="s">
-        <v>91</v>
-      </c>
-      <c r="M34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="11"/>
-      <c r="L35" t="s">
-        <v>91</v>
-      </c>
-      <c r="M35" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="6" t="s">
+      <c r="F37" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" s="21"/>
+      <c r="H37" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G38" s="21"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="16"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G39" s="21"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="12"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="C40" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D40" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="G40" s="21"/>
+      <c r="H40" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="15"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" s="21"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="16"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F37" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="10"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="11"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G39" s="9"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="12"/>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="G42" s="21"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="10" t="s">
+      <c r="D43" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="I40" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="10"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G41" s="9"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="11"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="12"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
+      <c r="E43" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="F43" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="10" t="s">
+      <c r="G43" s="21"/>
+      <c r="H43" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="G44" s="21"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="16"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="10"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="11"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="12"/>
-    </row>
-    <row r="46" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-    </row>
-    <row r="47" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
-    </row>
-    <row r="48" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
-    </row>
-    <row r="49" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="24"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-    </row>
-    <row r="50" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="24"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-    </row>
-    <row r="51" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="24"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="24"/>
-    </row>
-    <row r="52" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="24"/>
-    </row>
-    <row r="53" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="24"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="24"/>
-    </row>
-    <row r="54" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="24"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="24"/>
-    </row>
-    <row r="55" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="24"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="24"/>
-    </row>
-    <row r="56" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="24"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="24"/>
-      <c r="K56" s="24"/>
-    </row>
-    <row r="57" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="24"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="24"/>
-      <c r="K57" s="24"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+    </row>
+    <row r="47" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+    </row>
+    <row r="48" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="49" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+    </row>
+    <row r="50" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+    </row>
+    <row r="51" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+    </row>
+    <row r="52" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+    </row>
+    <row r="53" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+    </row>
+    <row r="54" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+    </row>
+    <row r="55" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+    </row>
+    <row r="56" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+    </row>
+    <row r="57" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="150">
-    <mergeCell ref="K43:K45"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="H43:H45"/>
-    <mergeCell ref="I43:I45"/>
-    <mergeCell ref="J43:J45"/>
-    <mergeCell ref="K37:K39"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="I40:I42"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="K40:K42"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="H37:H39"/>
-    <mergeCell ref="I37:I39"/>
-    <mergeCell ref="J37:J39"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="H34:H36"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="K34:K36"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="K31:K33"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="J28:J30"/>
+    <mergeCell ref="K28:K30"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="K25:K27"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A4:A6"/>
     <mergeCell ref="K4:K6"/>
     <mergeCell ref="K19:K21"/>
     <mergeCell ref="E2:E3"/>
@@ -2076,90 +2097,49 @@
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="K7:K9"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="K22:K24"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="K25:K27"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="J28:J30"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="K31:K33"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="H34:H36"/>
-    <mergeCell ref="I34:I36"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="K34:K36"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="K37:K39"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="I40:I42"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="K40:K42"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="I37:I39"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="K43:K45"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="H43:H45"/>
+    <mergeCell ref="I43:I45"/>
+    <mergeCell ref="J43:J45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
